--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVI/LTAIPT_A63F26.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXVI/LTAIPT_A63F26.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -13,20 +13,22 @@
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
     <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
+    <sheet name="Hidden_6" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="Hidden_18">Hidden_1!$A$1:$A$2</definedName>
-    <definedName name="Hidden_210">Hidden_2!$A$1:$A$2</definedName>
-    <definedName name="Hidden_311">Hidden_3!$A$1:$A$9</definedName>
-    <definedName name="Hidden_425">Hidden_4!$A$1:$A$2</definedName>
+    <definedName name="Hidden_17">Hidden_1!$A$1:$A$2</definedName>
+    <definedName name="Hidden_29">Hidden_2!$A$1:$A$2</definedName>
+    <definedName name="Hidden_311">Hidden_3!$A$1:$A$2</definedName>
+    <definedName name="Hidden_412">Hidden_4!$A$1:$A$9</definedName>
     <definedName name="Hidden_526">Hidden_5!$A$1:$A$2</definedName>
+    <definedName name="Hidden_627">Hidden_6!$A$1:$A$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="103">
   <si>
     <t>48980</t>
   </si>
@@ -88,6 +90,9 @@
     <t>436359</t>
   </si>
   <si>
+    <t>571933</t>
+  </si>
+  <si>
     <t>436342</t>
   </si>
   <si>
@@ -181,6 +186,9 @@
     <t>Segundo apellido de la persona que recibió los recursos del beneficiario</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Denominación o razón social del beneficiario</t>
   </si>
   <si>
@@ -253,7 +261,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -262,28 +270,28 @@
     <t>Departamento de contabilidad</t>
   </si>
   <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
     <t>02/04/2018</t>
   </si>
   <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>61B71715C3155DCFD7E1CBD5816A02DF</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de enero de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos y a las personas físicas o morales que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier motivo.</t>
-  </si>
-  <si>
-    <t>50BE56DF2B620EFE479B22E036D6874E</t>
-  </si>
-  <si>
-    <t>947BE940C29626AEF35DAB292B59D30C</t>
+    <t>5B628DBBFED1DBD1FB7DAACBE5168245</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de abril de 2023 al 30 de junio de 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos y a las personas físicas o morales que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier motivo.</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Persona física</t>
@@ -721,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE10"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
@@ -731,38 +739,39 @@
     <col min="5" max="5" width="55.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="61" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="53" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="63.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="50.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="56.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="73.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="75.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="63.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="60.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="255" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="52.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="53" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="63.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="50.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="56.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="73.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="63.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -779,7 +788,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -794,7 +803,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -814,79 +823,82 @@
         <v>6</v>
       </c>
       <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>8</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>8</v>
       </c>
       <c r="L4" t="s">
         <v>8</v>
       </c>
       <c r="M4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
       </c>
       <c r="O4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P4" t="s">
         <v>10</v>
       </c>
       <c r="Q4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R4" t="s">
         <v>6</v>
       </c>
       <c r="S4" t="s">
+        <v>6</v>
+      </c>
+      <c r="T4" t="s">
         <v>7</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>11</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>7</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>11</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>6</v>
-      </c>
-      <c r="X4" t="s">
-        <v>7</v>
       </c>
       <c r="Y4" t="s">
         <v>7</v>
       </c>
       <c r="Z4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4" t="s">
         <v>8</v>
       </c>
       <c r="AB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>12</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>14</v>
       </c>
@@ -977,10 +989,13 @@
       <c r="AE5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -1012,387 +1027,204 @@
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
-    </row>
-    <row r="7" spans="1:31" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AF6" s="4"/>
+    </row>
+    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="AF7" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="X9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE9" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="AF8" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Z10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AB10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AC10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE10" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AE6"/>
+    <mergeCell ref="A6:AF6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1400,21 +1232,24 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I8:I193">
-      <formula1>Hidden_18</formula1>
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H8:H199">
+      <formula1>Hidden_17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K193">
-      <formula1>Hidden_210</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J199">
+      <formula1>Hidden_29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L193">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L199">
       <formula1>Hidden_311</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z8:Z193">
-      <formula1>Hidden_425</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="M8:M199">
+      <formula1>Hidden_412</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA8:AA193">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA8:AA199">
       <formula1>Hidden_526</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB8:AB199">
+      <formula1>Hidden_627</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1463,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1474,41 +1309,6 @@
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1518,16 +1318,51 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1543,12 +1378,32 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
